--- a/artfynd/A 32165-2019 artfynd.xlsx
+++ b/artfynd/A 32165-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32165-2019 artfynd.xlsx
+++ b/artfynd/A 32165-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1743,6 +1743,120 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124955940</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56965</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>O om Bräntberget, Orrböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>728407</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7105303</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32165-2019 artfynd.xlsx
+++ b/artfynd/A 32165-2019 artfynd.xlsx
@@ -1748,7 +1748,7 @@
         <v>124955940</v>
       </c>
       <c r="B11" t="n">
-        <v>56965</v>
+        <v>57053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32165-2019 artfynd.xlsx
+++ b/artfynd/A 32165-2019 artfynd.xlsx
@@ -1750,11 +1750,6 @@
       <c r="B11" t="n">
         <v>57053</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>LC</t>
